--- a/content/xls/NSO_01.01.2026.xlsx
+++ b/content/xls/NSO_01.01.2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E03E51E-E885-422B-97AE-34E0858426E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461D154B-F093-4F3B-A5FF-181C225CDCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -42,40 +42,37 @@
     <t>Численность населения, чел.</t>
   </si>
   <si>
-    <t>Уровень потребности в развитии дистанционного банковского обслуживания (Уровень потребности в ДБО)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уровень потребности в ДБО с учетом созданной альтернативной инфраструктуры </t>
-  </si>
-  <si>
     <t>Количество точек финансового доступа</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников 
-(учет ведется в разрезе населенных пунктов, в которых проживают Финансовые помощники)</t>
-  </si>
-  <si>
-    <t>Количество точек с банковским работником 
-(головной офис банка, его филиал или внутреннее структурное подразделение; мобильный банковский офис; удаленная точка с банковским работником)</t>
-  </si>
-  <si>
-    <t>Количество Отделений почтовой связи
-(стационарные отделения почтовой связи, передвижные отделения почтовой связи)</t>
-  </si>
-  <si>
-    <t>Количество банкоматов с функцией выдача наличных</t>
-  </si>
-  <si>
-    <t>Количество торгово-сервисных предприятий с сервисом "Выдача наличных на кассе"</t>
-  </si>
-  <si>
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
     <t>Новосибирская область</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в ДБО за счет создания альтернативной инфраструктуры</t>
+    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры (Уровень потребности в ДБО)</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в ДБО с учетом альтернативной инфраструктуры</t>
+  </si>
+  <si>
+    <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
+  </si>
+  <si>
+    <t>Количество Финансовых помощников</t>
+  </si>
+  <si>
+    <t>Количество торговых точек с сервисом "Выдача наличных на кассе"</t>
+  </si>
+  <si>
+    <t>Количество банков</t>
+  </si>
+  <si>
+    <t>Количество Отделений почтовой связи</t>
+  </si>
+  <si>
+    <t>Количество банкоматов</t>
   </si>
 </sst>
 </file>
@@ -104,7 +101,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -149,22 +146,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -496,80 +501,80 @@
     <col min="12" max="12" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="98.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" ht="103.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="B2" s="1">
-        <v>741395</v>
-      </c>
-      <c r="C2" s="4">
+        <v>741397</v>
+      </c>
+      <c r="C2" s="3">
         <v>0.19046803652968025</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>2.9083333333333333E-2</v>
       </c>
-      <c r="E2" s="4">
-        <v>0.16138470319634748</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="G2" s="7">
         <v>2</v>
       </c>
-      <c r="G2" s="5">
-        <v>35</v>
-      </c>
-      <c r="H2" s="5">
-        <v>217</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="H2" s="7">
+        <v>12</v>
+      </c>
+      <c r="I2" s="8">
+        <v>187</v>
+      </c>
+      <c r="J2" s="8">
+        <v>14</v>
+      </c>
+      <c r="K2" s="8">
         <v>540</v>
       </c>
-      <c r="J2" s="5">
+      <c r="L2" s="8">
         <v>343</v>
-      </c>
-      <c r="K2" s="5">
-        <v>187</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0.80953196347031919</v>
       </c>
     </row>
   </sheetData>

--- a/content/xls/NSO_01.01.2026.xlsx
+++ b/content/xls/NSO_01.01.2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461D154B-F093-4F3B-A5FF-181C225CDCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45F9880-F465-499D-9DCA-289785DDD66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -544,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>741397</v>
+        <v>741396</v>
       </c>
       <c r="C2" s="3">
         <v>0.19046803652968025</v>

--- a/content/xls/NSO_01.01.2026.xlsx
+++ b/content/xls/NSO_01.01.2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45F9880-F465-499D-9DCA-289785DDD66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACB09E0-F4E2-42D3-A230-2E008BDA8932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -51,12 +51,6 @@
     <t>Новосибирская область</t>
   </si>
   <si>
-    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры (Уровень потребности в ДБО)</t>
-  </si>
-  <si>
-    <t>Изменение уровня потребности в ДБО с учетом альтернативной инфраструктуры</t>
-  </si>
-  <si>
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
@@ -73,6 +67,12 @@
   </si>
   <si>
     <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
@@ -490,7 +490,7 @@
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
@@ -509,34 +509,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">

--- a/content/xls/NSO_01.01.2026.xlsx
+++ b/content/xls/NSO_01.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACB09E0-F4E2-42D3-A230-2E008BDA8932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED42174-CF3E-41C8-9C16-4165B5892288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="4702" yWindow="4702" windowWidth="23630" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="page1" sheetId="1" r:id="rId1"/>
@@ -72,21 +72,37 @@
     <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
   </si>
   <si>
-    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_-\ #,##0.0_-;\-\ #,##0.0_-;_-\ &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,38 +159,59 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -490,7 +527,7 @@
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" customWidth="1"/>
     <col min="5" max="5" width="22.109375" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="28.77734375" customWidth="1"/>
@@ -501,83 +538,96 @@
     <col min="12" max="12" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="103.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" ht="118.15" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
-        <v>741396</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.19046803652968025</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2.9083333333333333E-2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.81</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="G2" s="7">
-        <v>2</v>
-      </c>
-      <c r="H2" s="7">
-        <v>12</v>
-      </c>
-      <c r="I2" s="8">
-        <v>187</v>
-      </c>
-      <c r="J2" s="8">
-        <v>14</v>
-      </c>
-      <c r="K2" s="8">
-        <v>540</v>
-      </c>
-      <c r="L2" s="8">
-        <v>343</v>
+      <c r="B2" s="4">
+        <v>720534</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="F2" s="7">
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8">
+        <v>35</v>
+      </c>
+      <c r="I2" s="9">
+        <v>216</v>
+      </c>
+      <c r="J2" s="9">
+        <v>217</v>
+      </c>
+      <c r="K2" s="9">
+        <v>555</v>
+      </c>
+      <c r="L2" s="9">
+        <v>377</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/content/xls/NSO_01.01.2026.xlsx
+++ b/content/xls/NSO_01.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED42174-CF3E-41C8-9C16-4165B5892288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E19518F-77E4-40E1-B435-65668EC4EE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4702" yWindow="4702" windowWidth="23630" windowHeight="8566" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="page1" sheetId="1" r:id="rId1"/>
@@ -587,7 +587,7 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D2" s="6">
-        <v>2.9</v>
+        <v>-2.9</v>
       </c>
       <c r="E2" s="5">
         <v>0.80500000000000005</v>

--- a/content/xls/NSO_01.01.2026.xlsx
+++ b/content/xls/NSO_01.01.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E19518F-77E4-40E1-B435-65668EC4EE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CF968D-98DD-4394-99A2-0683388508E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников</t>
-  </si>
-  <si>
     <t>Количество торговых точек с сервисом "Выдача наличных на кассе"</t>
   </si>
   <si>
@@ -73,6 +70,9 @@
   </si>
   <si>
     <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
   </si>
 </sst>
 </file>
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -561,19 +561,19 @@
         <v>2</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
